--- a/artfynd/A 50008-2020 artfynd.xlsx
+++ b/artfynd/A 50008-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50008-2020 artfynd.xlsx
+++ b/artfynd/A 50008-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104159660</v>
+        <v>104159659</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661963.1780866608</v>
+        <v>661977.6169560454</v>
       </c>
       <c r="R6" t="n">
-        <v>7219089.471081461</v>
+        <v>7219057.688472058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159659</v>
+        <v>104159669</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661977.6169560454</v>
+        <v>661943.9242654756</v>
       </c>
       <c r="R7" t="n">
-        <v>7219057.688472058</v>
+        <v>7219093.073653187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104159669</v>
+        <v>104159668</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661943.9242654756</v>
+        <v>661936.6638948423</v>
       </c>
       <c r="R8" t="n">
-        <v>7219093.073653187</v>
+        <v>7219125.247531212</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104159668</v>
+        <v>109909884</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
+        <v>96334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kristineberg, Ly lm</t>
+          <t>Björksele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661936.6638948423</v>
+        <v>661978.4614438319</v>
       </c>
       <c r="R9" t="n">
-        <v>7219125.247531212</v>
+        <v>7219057.73454546</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109909884</v>
+        <v>109909885</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
+        <v>77506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661978.4614438319</v>
+        <v>661961.9573823668</v>
       </c>
       <c r="R10" t="n">
-        <v>7219057.73454546</v>
+        <v>7219088.558510034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109909885</v>
+        <v>109909890</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661961.9573823668</v>
+        <v>661940.0551047546</v>
       </c>
       <c r="R11" t="n">
-        <v>7219088.558510034</v>
+        <v>7219094.131568091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109909890</v>
+        <v>109909888</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
+        <v>89952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,25 +1857,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661940.0551047546</v>
+        <v>661841.2730650033</v>
       </c>
       <c r="R12" t="n">
-        <v>7219094.131568091</v>
+        <v>7219235.940911839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109909888</v>
+        <v>112610283</v>
       </c>
       <c r="B13" t="n">
-        <v>89952</v>
+        <v>89789</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661841.2730650033</v>
+        <v>661940</v>
       </c>
       <c r="R13" t="n">
-        <v>7219235.940911839</v>
+        <v>7219094</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,19 +2035,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2079,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112606338</v>
+        <v>112610280</v>
       </c>
       <c r="B14" t="n">
-        <v>77856</v>
+        <v>89771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,34 +2085,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kristineberg, Ly lm</t>
+          <t>Björksele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661978</v>
+        <v>661841</v>
       </c>
       <c r="R14" t="n">
-        <v>7219058</v>
+        <v>7219236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112610283</v>
+        <v>112610276</v>
       </c>
       <c r="B15" t="n">
-        <v>89789</v>
+        <v>78919</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,21 +2192,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2226,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661940</v>
+        <v>661962</v>
       </c>
       <c r="R15" t="n">
-        <v>7219094</v>
+        <v>7219089</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,862 +2280,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112606340</v>
-      </c>
-      <c r="B16" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>661867</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7219221</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112610280</v>
-      </c>
-      <c r="B17" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Björksele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>661841</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7219236</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112606345</v>
-      </c>
-      <c r="B18" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>661937</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7219125</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112610276</v>
-      </c>
-      <c r="B19" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Björksele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>661962</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7219089</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112606339</v>
-      </c>
-      <c r="B20" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>661963</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7219089</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112606343</v>
-      </c>
-      <c r="B21" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>661839</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7219239</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112606341</v>
-      </c>
-      <c r="B22" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>661822</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7219294</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112606346</v>
-      </c>
-      <c r="B23" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Kristineberg, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>661944</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7219093</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
